--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>79.13777560653226</v>
+        <v>12.85988853606149</v>
       </c>
       <c r="D2" t="n">
-        <v>79.70968284260427</v>
+        <v>12.95282346192319</v>
       </c>
       <c r="E2" t="n">
-        <v>20.20155636978711</v>
+        <v>3.282752910090405</v>
       </c>
       <c r="F2" t="n">
-        <v>22.58193031009573</v>
+        <v>3.669563675390556</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>57.49644234390874</v>
+        <v>9.343171880885171</v>
       </c>
       <c r="D3" t="n">
-        <v>52.24201389789471</v>
+        <v>8.48932725840789</v>
       </c>
       <c r="E3" t="n">
-        <v>20.20155636978711</v>
+        <v>3.282752910090405</v>
       </c>
       <c r="F3" t="n">
-        <v>22.58193031009573</v>
+        <v>3.669563675390556</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.65329748387931</v>
+        <v>4.006160841130389</v>
       </c>
       <c r="D4" t="n">
-        <v>20.81885383000871</v>
+        <v>3.383063747376415</v>
       </c>
       <c r="E4" t="n">
-        <v>20.20155636978711</v>
+        <v>3.282752910090405</v>
       </c>
       <c r="F4" t="n">
-        <v>22.58193031009573</v>
+        <v>3.669563675390556</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>67.65647772147528</v>
+        <v>10.99417762973973</v>
       </c>
       <c r="D5" t="n">
-        <v>34.06164947306241</v>
+        <v>5.535018039372642</v>
       </c>
       <c r="E5" t="n">
-        <v>20.20155636978711</v>
+        <v>3.282752910090405</v>
       </c>
       <c r="F5" t="n">
-        <v>22.58193031009573</v>
+        <v>3.669563675390556</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>79.33067905936481</v>
+        <v>12.89123534714678</v>
       </c>
       <c r="D6" t="n">
-        <v>19.32640854866406</v>
+        <v>3.140541389157909</v>
       </c>
       <c r="E6" t="n">
-        <v>20.20155636978711</v>
+        <v>3.282752910090405</v>
       </c>
       <c r="F6" t="n">
-        <v>22.58193031009573</v>
+        <v>3.669563675390556</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
